--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -365,15 +365,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -396,6 +387,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,11 +777,11 @@
     </row>
     <row r="2" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -789,11 +789,11 @@
     </row>
     <row r="3" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="35">
+      <c r="B3" s="43">
         <v>2025</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -810,15 +810,15 @@
       <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -959,15 +959,15 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="3"/>
       <c r="I10" s="12" t="s">
         <v>2</v>
@@ -1008,13 +1008,13 @@
         <v>8</v>
       </c>
       <c r="H11" s="7"/>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="33" t="s">
         <v>38</v>
       </c>
       <c r="L11" s="2">
@@ -1054,7 +1054,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39">
+      <c r="A13" s="36">
         <v>3</v>
       </c>
       <c r="B13" s="7">
@@ -1063,7 +1063,7 @@
       <c r="C13" s="7">
         <v>5</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="35">
         <v>6</v>
       </c>
       <c r="E13" s="7">
@@ -1093,7 +1093,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42">
+      <c r="A14" s="39">
         <v>10</v>
       </c>
       <c r="B14" s="7">
@@ -1102,7 +1102,7 @@
       <c r="C14" s="7">
         <v>12</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="37">
         <v>13</v>
       </c>
       <c r="E14" s="7">
@@ -1132,7 +1132,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="38">
         <v>17</v>
       </c>
       <c r="B15" s="7">
@@ -1141,7 +1141,7 @@
       <c r="C15" s="7">
         <v>19</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="37">
         <v>20</v>
       </c>
       <c r="E15" s="7">
@@ -1180,7 +1180,7 @@
       <c r="C16" s="7">
         <v>26</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="40">
         <v>27</v>
       </c>
       <c r="E16" s="7">
@@ -1235,15 +1235,15 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="7"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>

--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -189,7 +189,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,12 +256,6 @@
         <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -275,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,13 +374,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -777,11 +765,11 @@
     </row>
     <row r="2" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -789,11 +777,11 @@
     </row>
     <row r="3" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="43">
+      <c r="B3" s="41">
         <v>2025</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -810,15 +798,15 @@
       <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -959,15 +947,15 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="3"/>
       <c r="I10" s="12" t="s">
         <v>2</v>
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="38">
         <v>10</v>
       </c>
       <c r="B14" s="7">
@@ -1132,7 +1120,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38">
+      <c r="A15" s="10">
         <v>17</v>
       </c>
       <c r="B15" s="7">
@@ -1180,7 +1168,7 @@
       <c r="C16" s="7">
         <v>26</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="38">
         <v>27</v>
       </c>
       <c r="E16" s="7">
@@ -1235,15 +1223,15 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="7"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>

--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Spring" sheetId="1" r:id="rId1"/>
+    <sheet name="2026" sheetId="2" r:id="rId1"/>
+    <sheet name="Spring" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="49">
   <si>
     <t>Multivar</t>
   </si>
@@ -141,6 +142,36 @@
   </si>
   <si>
     <t>А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тест Мантела, ANOSIM, SIMPER, PERMANOVA </t>
+  </si>
+  <si>
+    <t>2 мар</t>
+  </si>
+  <si>
+    <t>5 мар</t>
+  </si>
+  <si>
+    <t>9 мар</t>
+  </si>
+  <si>
+    <t>12 мар</t>
+  </si>
+  <si>
+    <t>2 апр</t>
+  </si>
+  <si>
+    <t>6 апр</t>
+  </si>
+  <si>
+    <t>9 апр</t>
+  </si>
+  <si>
+    <t>16 мар</t>
+  </si>
+  <si>
+    <t>23 мар</t>
   </si>
 </sst>
 </file>
@@ -189,7 +220,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +287,36 @@
         <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -269,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,11 +441,63 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,6 +850,674 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:M31"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
+    <col min="4" max="4" width="3.44140625" customWidth="1"/>
+    <col min="5" max="5" width="3.6640625" customWidth="1"/>
+    <col min="6" max="6" width="3.77734375" customWidth="1"/>
+    <col min="7" max="7" width="4.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A2" s="39"/>
+      <c r="B2" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A3" s="39"/>
+      <c r="B3" s="42">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="9">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>16</v>
+      </c>
+      <c r="B7" s="44">
+        <v>17</v>
+      </c>
+      <c r="C7" s="44">
+        <v>18</v>
+      </c>
+      <c r="D7" s="43">
+        <v>19</v>
+      </c>
+      <c r="E7" s="44">
+        <v>20</v>
+      </c>
+      <c r="F7" s="44">
+        <v>21</v>
+      </c>
+      <c r="G7" s="44">
+        <v>22</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="9">
+        <v>2</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>23</v>
+      </c>
+      <c r="B8" s="44">
+        <v>24</v>
+      </c>
+      <c r="C8" s="44">
+        <v>25</v>
+      </c>
+      <c r="D8" s="45">
+        <v>26</v>
+      </c>
+      <c r="E8" s="46">
+        <v>27</v>
+      </c>
+      <c r="F8" s="44">
+        <v>28</v>
+      </c>
+      <c r="G8" s="44"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="9">
+        <v>3</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="47"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="9">
+        <v>4</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="9">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="2">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="9">
+        <v>7</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="49">
+        <v>2</v>
+      </c>
+      <c r="B13" s="44">
+        <v>3</v>
+      </c>
+      <c r="C13" s="44">
+        <v>4</v>
+      </c>
+      <c r="D13" s="51">
+        <v>5</v>
+      </c>
+      <c r="E13" s="44">
+        <v>6</v>
+      </c>
+      <c r="F13" s="44">
+        <v>7</v>
+      </c>
+      <c r="G13" s="44">
+        <v>8</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="9">
+        <v>8</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="50">
+        <v>9</v>
+      </c>
+      <c r="B14" s="44">
+        <v>10</v>
+      </c>
+      <c r="C14" s="44">
+        <v>11</v>
+      </c>
+      <c r="D14" s="50">
+        <v>12</v>
+      </c>
+      <c r="E14" s="44">
+        <v>13</v>
+      </c>
+      <c r="F14" s="44">
+        <v>14</v>
+      </c>
+      <c r="G14" s="44">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="16">
+        <v>9</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="43">
+        <v>16</v>
+      </c>
+      <c r="B15" s="44">
+        <v>17</v>
+      </c>
+      <c r="C15" s="44">
+        <v>18</v>
+      </c>
+      <c r="D15" s="43">
+        <v>19</v>
+      </c>
+      <c r="E15" s="44">
+        <v>20</v>
+      </c>
+      <c r="F15" s="44">
+        <v>21</v>
+      </c>
+      <c r="G15" s="44">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="9">
+        <v>10</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
+        <v>23</v>
+      </c>
+      <c r="B16" s="44">
+        <v>24</v>
+      </c>
+      <c r="C16" s="44">
+        <v>25</v>
+      </c>
+      <c r="D16" s="43">
+        <v>26</v>
+      </c>
+      <c r="E16" s="44">
+        <v>27</v>
+      </c>
+      <c r="F16" s="44">
+        <v>28</v>
+      </c>
+      <c r="G16" s="44">
+        <v>29</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="9">
+        <v>11</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="43">
+        <v>30</v>
+      </c>
+      <c r="B17" s="44">
+        <v>31</v>
+      </c>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="44">
+        <v>1</v>
+      </c>
+      <c r="D20" s="36">
+        <v>2</v>
+      </c>
+      <c r="E20" s="44">
+        <v>3</v>
+      </c>
+      <c r="F20" s="44">
+        <v>4</v>
+      </c>
+      <c r="G20" s="44">
+        <v>5</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="50">
+        <v>6</v>
+      </c>
+      <c r="B21" s="47">
+        <v>7</v>
+      </c>
+      <c r="C21" s="44">
+        <v>8</v>
+      </c>
+      <c r="D21" s="38">
+        <v>9</v>
+      </c>
+      <c r="E21" s="44">
+        <v>10</v>
+      </c>
+      <c r="F21" s="44">
+        <v>11</v>
+      </c>
+      <c r="G21" s="44">
+        <v>12</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="50">
+        <v>13</v>
+      </c>
+      <c r="B22" s="47">
+        <v>14</v>
+      </c>
+      <c r="C22" s="44">
+        <v>15</v>
+      </c>
+      <c r="D22" s="49">
+        <v>16</v>
+      </c>
+      <c r="E22" s="44">
+        <v>17</v>
+      </c>
+      <c r="F22" s="44">
+        <v>18</v>
+      </c>
+      <c r="G22" s="44">
+        <v>19</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>20</v>
+      </c>
+      <c r="B23" s="47">
+        <v>21</v>
+      </c>
+      <c r="C23" s="44">
+        <v>22</v>
+      </c>
+      <c r="D23" s="36">
+        <v>23</v>
+      </c>
+      <c r="E23" s="44">
+        <v>24</v>
+      </c>
+      <c r="F23" s="44">
+        <v>25</v>
+      </c>
+      <c r="G23" s="44">
+        <v>26</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="44">
+        <v>27</v>
+      </c>
+      <c r="B24" s="47">
+        <v>28</v>
+      </c>
+      <c r="C24" s="44">
+        <v>29</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L31" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AMJ24"/>
   <sheetFormatPr defaultColWidth="6.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -765,11 +1546,11 @@
     </row>
     <row r="2" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -777,11 +1558,11 @@
     </row>
     <row r="3" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="41">
+      <c r="B3" s="42">
         <v>2025</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -798,15 +1579,15 @@
       <c r="M4" s="5"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -947,15 +1728,15 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
       <c r="H10" s="3"/>
       <c r="I10" s="12" t="s">
         <v>2</v>
@@ -1223,15 +2004,15 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="7"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
